--- a/uploads/Schema societario GE - Tri Star.xlsx
+++ b/uploads/Schema societario GE - Tri Star.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\GREEN ENERBRAS ONE SCSp\BRASILE\TRI STAR ENERGY LTDA (GP)\Schema Societario\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\GREEN ENERBRAS ONE SCSp\Schema Societario\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE7EFE36-7DDB-4629-95A5-FB16C4606630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{843E1A66-3D65-4D69-A713-ABAC9AFF6869}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{41CFF4C8-D23B-40BA-B97D-112330980BCA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{41CFF4C8-D23B-40BA-B97D-112330980BCA}"/>
   </bookViews>
   <sheets>
     <sheet name="Schema GREEN ENERBRAS" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,8 @@
   </sheets>
   <definedNames>
     <definedName name="Anniversaire">#REF!,#REF!,#REF!,#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Schema GREEN ENERBRAS'!$A$1:$T$42</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Schema GREEN ENERBRAS anonimo'!$A$1:$T$42</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Schema GREEN ENERBRAS'!$A$1:$T$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Schema GREEN ENERBRAS anonimo'!$A$1:$T$38</definedName>
     <definedName name="CAP1E">#REF!</definedName>
     <definedName name="CapitFIXE">#REF!</definedName>
     <definedName name="Changement_de_taux">#REF!</definedName>
@@ -518,13 +518,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>749300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>123826</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -568,13 +568,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>407670</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>123824</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>255270</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>103504</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -702,13 +702,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>123824</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>47624</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -749,13 +749,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>127001</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -859,13 +859,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>130175</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -913,13 +913,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>577850</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>146050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>263525</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>117475</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -965,13 +965,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>504824</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>104774</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>657224</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1068,13 +1068,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>123826</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>352424</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1161,13 +1161,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>130175</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1215,13 +1215,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>9524</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1262,13 +1262,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>9524</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1365,13 +1365,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1417,13 +1417,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>272114</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>81213</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1466,13 +1466,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>146050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1520,13 +1520,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>485773</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1567,13 +1567,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>142876</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1614,13 +1614,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>357839</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>90738</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1663,13 +1663,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>495299</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>19049</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>247649</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1763,13 +1763,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>155575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -1817,13 +1817,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>238124</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>142874</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>95249</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>19049</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1864,13 +1864,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>152401</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1907,6 +1907,106 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>628650</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>47624</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Immagine 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB8E6358-260A-DE99-D416-6197AF2316F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5753100" y="3543300"/>
+          <a:ext cx="5867399" cy="2933700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>190501</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>77720</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>9526</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>47954</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="26" name="Immagine 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE2CAE7F-D5CB-0778-3EEC-57D6B14E1E5B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1876426" y="1049270"/>
+          <a:ext cx="2495550" cy="779859"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -1916,13 +2016,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>749300</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>123826</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
       <xdr:colOff>200025</xdr:colOff>
-      <xdr:row>22</xdr:row>
+      <xdr:row>20</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1966,13 +2066,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>407670</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>123824</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>255270</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>103504</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2100,13 +2200,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>123824</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>9525</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>47624</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2147,13 +2247,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>127001</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2257,13 +2357,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>581025</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>12700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>130175</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2311,13 +2411,13 @@
     <xdr:from>
       <xdr:col>11</xdr:col>
       <xdr:colOff>577850</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>2</xdr:row>
       <xdr:rowOff>146050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>263525</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>117475</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2363,13 +2463,13 @@
     <xdr:from>
       <xdr:col>8</xdr:col>
       <xdr:colOff>504824</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>104774</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>657224</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2466,13 +2566,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>123826</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>352424</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2559,13 +2659,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>685800</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>352425</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>130175</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2613,13 +2713,13 @@
     <xdr:from>
       <xdr:col>7</xdr:col>
       <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
       <xdr:colOff>9524</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2660,13 +2760,13 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>9524</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2763,13 +2863,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>219075</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>666750</xdr:colOff>
-      <xdr:row>16</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2815,13 +2915,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>272114</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>81213</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2864,13 +2964,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>28575</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>146050</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -2918,13 +3018,13 @@
     <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>485773</xdr:colOff>
-      <xdr:row>30</xdr:row>
+      <xdr:row>28</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>9524</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -2965,13 +3065,13 @@
     <xdr:from>
       <xdr:col>10</xdr:col>
       <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>114300</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>676275</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>142876</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3012,13 +3112,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>21</xdr:row>
+      <xdr:row>19</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>357839</xdr:colOff>
-      <xdr:row>27</xdr:row>
+      <xdr:row>25</xdr:row>
       <xdr:rowOff>90738</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3061,13 +3161,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>495299</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>19049</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>247649</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3161,13 +3261,13 @@
     <xdr:from>
       <xdr:col>9</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>35</xdr:row>
+      <xdr:row>33</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>34</xdr:row>
       <xdr:rowOff>155575</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -3215,13 +3315,13 @@
     <xdr:from>
       <xdr:col>6</xdr:col>
       <xdr:colOff>238124</xdr:colOff>
-      <xdr:row>29</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>142874</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>95249</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>19049</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3262,13 +3362,13 @@
     <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>123825</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>152401</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -3305,13 +3405,113 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>952499</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="24" name="Immagine 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{209CE206-1E14-4EE6-AE4B-461A7D78BD49}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5695950" y="3286125"/>
+          <a:ext cx="5867399" cy="2933700"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>314325</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>133350</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>132159</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="Immagine 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A20F7558-C4DB-4361-B32E-6EDF9C7BDB5F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2038350" y="971550"/>
+          <a:ext cx="2495550" cy="779859"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema di Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3349,7 +3549,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3455,7 +3655,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3597,7 +3797,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3608,10 +3808,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:S49"/>
+  <dimension ref="B1:S47"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="5.140625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.140625" style="2" customWidth="1"/>
     <col min="2" max="4" width="5" style="2" customWidth="1"/>
     <col min="5" max="5" width="8.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" style="2" customWidth="1"/>
@@ -3631,450 +3831,444 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B1" s="1"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
     </row>
     <row r="2" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B2" s="5"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="8"/>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="O3" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="50"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="J4" s="7"/>
-      <c r="K4" s="8"/>
+      <c r="L4" s="9"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="13"/>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B5" s="6"/>
-      <c r="O5" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="50"/>
+      <c r="O5" s="14"/>
+      <c r="R5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="13"/>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="L6" s="9"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="13"/>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="17"/>
+      <c r="L6" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="18">
+        <v>1000</v>
+      </c>
+      <c r="P6" s="19">
+        <f>O6/$O$21</f>
+        <v>3.8314176245210726E-3</v>
+      </c>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="S6" s="21"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="O7" s="14"/>
-      <c r="R7" s="15" t="s">
-        <v>1</v>
-      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="5"/>
+      <c r="J7" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="25"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="28">
+        <f>SUM(O6)</f>
+        <v>1000</v>
+      </c>
+      <c r="P7" s="9">
+        <f>SUM(P6)</f>
+        <v>3.8314176245210726E-3</v>
+      </c>
+      <c r="R7" s="12"/>
       <c r="S7" s="13"/>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="18">
-        <v>1000</v>
-      </c>
-      <c r="P8" s="19">
-        <f>O8/$O$23</f>
-        <v>3.8314176245210726E-3</v>
-      </c>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20" t="s">
-        <v>4</v>
-      </c>
-      <c r="S8" s="21"/>
+      <c r="B8" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="26"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" s="13"/>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="5"/>
-      <c r="J9" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="K9" s="25"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="28">
-        <f>SUM(O8)</f>
-        <v>1000</v>
-      </c>
-      <c r="P9" s="9">
-        <f>SUM(P8)</f>
-        <v>3.8314176245210726E-3</v>
-      </c>
-      <c r="R9" s="12"/>
-      <c r="S9" s="13"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="32"/>
+      <c r="O9" s="33">
+        <v>20000</v>
+      </c>
+      <c r="P9" s="11">
+        <f>O9/$O$21</f>
+        <v>7.662835249042145E-2</v>
+      </c>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="S9" s="34"/>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B10" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="26"/>
-      <c r="N10" s="27"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="11"/>
+      <c r="L10" s="32"/>
+      <c r="O10" s="33">
+        <v>20000</v>
+      </c>
+      <c r="P10" s="11">
+        <f t="shared" ref="P10:P18" si="0">O10/$O$21</f>
+        <v>7.662835249042145E-2</v>
+      </c>
       <c r="Q10" s="12"/>
-      <c r="R10" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="13"/>
+      <c r="R10" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="S10" s="34"/>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B11" s="1"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="7"/>
+      <c r="J11" s="1"/>
       <c r="L11" s="32"/>
       <c r="O11" s="33">
         <v>20000</v>
       </c>
       <c r="P11" s="11">
-        <f>O11/$O$23</f>
+        <f t="shared" si="0"/>
         <v>7.662835249042145E-2</v>
       </c>
       <c r="Q11" s="12"/>
       <c r="R11" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="S11" s="34"/>
+        <v>12</v>
+      </c>
+      <c r="S11" s="13"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="L12" s="32"/>
+      <c r="J12" s="35"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="27"/>
       <c r="O12" s="33">
         <v>20000</v>
       </c>
       <c r="P12" s="11">
-        <f t="shared" ref="P12:P20" si="0">O12/$O$23</f>
+        <f t="shared" si="0"/>
         <v>7.662835249042145E-2</v>
       </c>
       <c r="Q12" s="12"/>
       <c r="R12" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="S12" s="34"/>
+        <v>13</v>
+      </c>
+      <c r="S12" s="13"/>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="J13" s="1"/>
-      <c r="L13" s="32"/>
+      <c r="I13" s="22"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="27"/>
       <c r="O13" s="33">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="P13" s="11">
         <f t="shared" si="0"/>
-        <v>7.662835249042145E-2</v>
+        <v>0.1532567049808429</v>
       </c>
       <c r="Q13" s="12"/>
       <c r="R13" s="12" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S13" s="13"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="J14" s="35"/>
-      <c r="L14" s="36"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="27"/>
       <c r="O14" s="33">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="P14" s="11">
         <f t="shared" si="0"/>
-        <v>7.662835249042145E-2</v>
+        <v>0.1532567049808429</v>
       </c>
       <c r="Q14" s="12"/>
       <c r="R14" s="12" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="S14" s="13"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="I15" s="22"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="27"/>
+      <c r="B15" s="6"/>
       <c r="O15" s="33">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="P15" s="11">
         <f t="shared" si="0"/>
-        <v>0.1532567049808429</v>
+        <v>7.662835249042145E-2</v>
       </c>
       <c r="Q15" s="12"/>
       <c r="R15" s="12" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S15" s="13"/>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16" t="s">
+        <v>20</v>
+      </c>
       <c r="O16" s="33">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="P16" s="11">
         <f t="shared" si="0"/>
-        <v>0.1532567049808429</v>
+        <v>7.662835249042145E-2</v>
       </c>
       <c r="Q16" s="12"/>
       <c r="R16" s="12" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="S16" s="13"/>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B17" s="6"/>
+      <c r="B17" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="37">
+        <v>0.99781732000000001</v>
+      </c>
+      <c r="L17" s="23"/>
       <c r="O17" s="33">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="P17" s="11">
         <f t="shared" si="0"/>
-        <v>7.662835249042145E-2</v>
+        <v>0.1532567049808429</v>
       </c>
       <c r="Q17" s="12"/>
       <c r="R17" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="S17" s="13"/>
+        <v>24</v>
+      </c>
+      <c r="S17" s="34"/>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="O18" s="33">
+      <c r="B18" s="6"/>
+      <c r="I18" s="38"/>
+      <c r="O18" s="18">
         <v>20000</v>
       </c>
-      <c r="P18" s="11">
+      <c r="P18" s="19">
         <f t="shared" si="0"/>
         <v>7.662835249042145E-2</v>
       </c>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="S18" s="13"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="S18" s="39"/>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B19" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="16"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="K19" s="37">
-        <v>0.99781732000000001</v>
-      </c>
-      <c r="L19" s="23"/>
-      <c r="O19" s="33">
-        <v>40000</v>
-      </c>
-      <c r="P19" s="11">
-        <f t="shared" si="0"/>
-        <v>0.1532567049808429</v>
-      </c>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12" t="s">
-        <v>24</v>
+      <c r="J19" s="40"/>
+      <c r="O19" s="28">
+        <f>SUM(O9:O18)</f>
+        <v>260000</v>
+      </c>
+      <c r="P19" s="9">
+        <f>SUM(P9:P18)</f>
+        <v>0.99616858237547878</v>
       </c>
       <c r="S19" s="34"/>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B20" s="6"/>
-      <c r="I20" s="38"/>
-      <c r="O20" s="18">
-        <v>20000</v>
-      </c>
-      <c r="P20" s="19">
-        <f t="shared" si="0"/>
-        <v>7.662835249042145E-2</v>
-      </c>
+      <c r="O20" s="41"/>
+      <c r="P20" s="20"/>
       <c r="Q20" s="20"/>
-      <c r="R20" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="S20" s="39"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="21"/>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="J21" s="40"/>
-      <c r="O21" s="28">
-        <f>SUM(O11:O20)</f>
-        <v>260000</v>
-      </c>
-      <c r="P21" s="9">
-        <f>SUM(P11:P20)</f>
-        <v>0.99616858237547878</v>
-      </c>
-      <c r="S21" s="34"/>
+      <c r="O21" s="43">
+        <f>O7+O19</f>
+        <v>261000</v>
+      </c>
+      <c r="P21" s="44">
+        <f>P7+P19</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="Q21" s="42"/>
+      <c r="R21" s="42"/>
+      <c r="S21" s="21"/>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="O22" s="41"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="42"/>
-      <c r="S22" s="21"/>
-    </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="O23" s="43">
-        <f>O9+O21</f>
-        <v>261000</v>
-      </c>
-      <c r="P23" s="44">
-        <f>P9+P21</f>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="Q23" s="42"/>
-      <c r="R23" s="42"/>
-      <c r="S23" s="21"/>
+      <c r="I22" s="38"/>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="I24" s="38"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="O24" s="45"/>
+    </row>
+    <row r="25" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="22"/>
+      <c r="L25" s="16"/>
+      <c r="O25" s="46"/>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="12"/>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.2">
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="16"/>
+      <c r="I26" s="22"/>
       <c r="L26" s="16"/>
-      <c r="O26" s="45"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="12"/>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="22"/>
-      <c r="L27" s="16"/>
-      <c r="O27" s="46"/>
+      <c r="D27" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="O27" s="12"/>
       <c r="P27" s="12"/>
       <c r="Q27" s="12"/>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="22"/>
-      <c r="L28" s="16"/>
-      <c r="O28" s="46"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
+      <c r="J28" s="16"/>
+      <c r="O28" s="12"/>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="D29" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I29" s="12"/>
-      <c r="K29" s="12"/>
+      <c r="G29" s="6"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="22"/>
       <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="G30" s="6"/>
       <c r="J30" s="16"/>
-      <c r="O30" s="12"/>
+      <c r="L30" s="12"/>
     </row>
     <row r="31" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="G31" s="6"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="22"/>
-      <c r="O31" s="12"/>
-    </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="G32" s="6"/>
-      <c r="J32" s="16"/>
-      <c r="L32" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="47"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="L33" s="12"/>
-      <c r="M33" s="22"/>
-      <c r="N33" s="5"/>
       <c r="O33" s="47"/>
     </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="L34" s="12"/>
+      <c r="O34" s="47"/>
+    </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="O35" s="47"/>
+      <c r="L35" s="12"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="L36" s="12"/>
-      <c r="O36" s="47"/>
+      <c r="E36" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="L37" s="12"/>
+      <c r="B37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O37" s="47"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="E38" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I38" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O39" s="47"/>
+      <c r="R38" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="R40" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="O42" s="47"/>
+      <c r="O40" s="47"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="O43" s="47"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="O45" s="47"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="O47" s="47"/>
-    </row>
-    <row r="49" spans="15:16" x14ac:dyDescent="0.2">
-      <c r="O49" s="47"/>
-      <c r="P49" s="16"/>
+      <c r="P47" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="O3:S3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="80" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="82" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -4085,7 +4279,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:S49"/>
+  <dimension ref="B1:S47"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="2.7109375" style="2" customWidth="1"/>
@@ -4108,450 +4302,444 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B1" s="1"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
     </row>
     <row r="2" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B2" s="5"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="8"/>
     </row>
     <row r="3" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="J3" s="6"/>
-      <c r="K3" s="6"/>
+      <c r="B3" s="6"/>
+      <c r="O3" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="P3" s="49"/>
+      <c r="Q3" s="49"/>
+      <c r="R3" s="49"/>
+      <c r="S3" s="50"/>
     </row>
     <row r="4" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="J4" s="7"/>
-      <c r="K4" s="8"/>
+      <c r="L4" s="9"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="11"/>
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12"/>
+      <c r="S4" s="13"/>
     </row>
     <row r="5" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B5" s="6"/>
-      <c r="O5" s="48" t="s">
-        <v>0</v>
-      </c>
-      <c r="P5" s="49"/>
-      <c r="Q5" s="49"/>
-      <c r="R5" s="49"/>
-      <c r="S5" s="50"/>
+      <c r="O5" s="14"/>
+      <c r="R5" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="S5" s="13"/>
     </row>
     <row r="6" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="L6" s="9"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="11"/>
-      <c r="Q6" s="12"/>
-      <c r="R6" s="12"/>
-      <c r="S6" s="13"/>
+      <c r="B6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="17"/>
+      <c r="L6" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="O6" s="18">
+        <v>1000</v>
+      </c>
+      <c r="P6" s="19">
+        <f>O6/$O$21</f>
+        <v>3.8314176245210726E-3</v>
+      </c>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="S6" s="21"/>
     </row>
     <row r="7" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="O7" s="14"/>
-      <c r="R7" s="15" t="s">
-        <v>1</v>
-      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="5"/>
+      <c r="J7" s="24" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="25"/>
+      <c r="M7" s="26"/>
+      <c r="N7" s="27"/>
+      <c r="O7" s="28">
+        <f>SUM(O6)</f>
+        <v>1000</v>
+      </c>
+      <c r="P7" s="9">
+        <f>SUM(P6)</f>
+        <v>3.8314176245210726E-3</v>
+      </c>
+      <c r="R7" s="12"/>
       <c r="S7" s="13"/>
     </row>
     <row r="8" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F8" s="16" t="s">
-        <v>2</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="17"/>
-      <c r="L8" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="O8" s="18">
-        <v>1000</v>
-      </c>
-      <c r="P8" s="19">
-        <f>O8/$O$23</f>
-        <v>3.8314176245210726E-3</v>
-      </c>
-      <c r="Q8" s="20"/>
-      <c r="R8" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="S8" s="21"/>
+      <c r="B8" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="26"/>
+      <c r="N8" s="27"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="11"/>
+      <c r="Q8" s="12"/>
+      <c r="R8" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="S8" s="13"/>
     </row>
     <row r="9" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B9" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="22"/>
-      <c r="F9" s="23"/>
-      <c r="G9" s="5"/>
-      <c r="J9" s="24" t="s">
-        <v>6</v>
-      </c>
-      <c r="K9" s="25"/>
-      <c r="M9" s="26"/>
-      <c r="N9" s="27"/>
-      <c r="O9" s="28">
-        <f>SUM(O8)</f>
-        <v>1000</v>
-      </c>
-      <c r="P9" s="9">
-        <f>SUM(P8)</f>
-        <v>3.8314176245210726E-3</v>
-      </c>
-      <c r="R9" s="12"/>
-      <c r="S9" s="13"/>
+      <c r="B9" s="1"/>
+      <c r="C9" s="32"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32"/>
+      <c r="G9" s="12"/>
+      <c r="H9" s="12"/>
+      <c r="I9" s="12"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="32"/>
+      <c r="O9" s="33">
+        <v>20000</v>
+      </c>
+      <c r="P9" s="11">
+        <f>O9/$O$21</f>
+        <v>7.662835249042145E-2</v>
+      </c>
+      <c r="Q9" s="12"/>
+      <c r="R9" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="S9" s="34"/>
     </row>
     <row r="10" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B10" s="24" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="29"/>
-      <c r="E10" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="26"/>
-      <c r="N10" s="27"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="11"/>
+      <c r="L10" s="32"/>
+      <c r="O10" s="33">
+        <v>20000</v>
+      </c>
+      <c r="P10" s="11">
+        <f t="shared" ref="P10:P18" si="0">O10/$O$21</f>
+        <v>7.662835249042145E-2</v>
+      </c>
       <c r="Q10" s="12"/>
-      <c r="R10" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="S10" s="13"/>
+      <c r="R10" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="S10" s="34"/>
     </row>
     <row r="11" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B11" s="1"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="12"/>
-      <c r="H11" s="12"/>
-      <c r="I11" s="12"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="7"/>
+      <c r="J11" s="1"/>
       <c r="L11" s="32"/>
       <c r="O11" s="33">
         <v>20000</v>
       </c>
       <c r="P11" s="11">
-        <f>O11/$O$23</f>
+        <f t="shared" si="0"/>
         <v>7.662835249042145E-2</v>
       </c>
       <c r="Q11" s="12"/>
       <c r="R11" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="S11" s="34"/>
+        <v>36</v>
+      </c>
+      <c r="S11" s="13"/>
     </row>
     <row r="12" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="L12" s="32"/>
+      <c r="J12" s="35"/>
+      <c r="L12" s="36"/>
+      <c r="M12" s="12"/>
+      <c r="N12" s="27"/>
       <c r="O12" s="33">
         <v>20000</v>
       </c>
       <c r="P12" s="11">
-        <f t="shared" ref="P12:P20" si="0">O12/$O$23</f>
+        <f t="shared" si="0"/>
         <v>7.662835249042145E-2</v>
       </c>
       <c r="Q12" s="12"/>
       <c r="R12" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="S12" s="34"/>
+        <v>37</v>
+      </c>
+      <c r="S12" s="13"/>
     </row>
     <row r="13" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="J13" s="1"/>
-      <c r="L13" s="32"/>
+      <c r="I13" s="22"/>
+      <c r="L13" s="36"/>
+      <c r="M13" s="12"/>
+      <c r="N13" s="27"/>
       <c r="O13" s="33">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="P13" s="11">
         <f t="shared" si="0"/>
-        <v>7.662835249042145E-2</v>
+        <v>0.1532567049808429</v>
       </c>
       <c r="Q13" s="12"/>
       <c r="R13" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="S13" s="13"/>
     </row>
     <row r="14" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="J14" s="35"/>
-      <c r="L14" s="36"/>
-      <c r="M14" s="12"/>
-      <c r="N14" s="27"/>
       <c r="O14" s="33">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="P14" s="11">
         <f t="shared" si="0"/>
-        <v>7.662835249042145E-2</v>
+        <v>0.1532567049808429</v>
       </c>
       <c r="Q14" s="12"/>
       <c r="R14" s="12" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="S14" s="13"/>
     </row>
     <row r="15" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="I15" s="22"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="12"/>
-      <c r="N15" s="27"/>
+      <c r="B15" s="6"/>
       <c r="O15" s="33">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="P15" s="11">
         <f t="shared" si="0"/>
-        <v>0.1532567049808429</v>
+        <v>7.662835249042145E-2</v>
       </c>
       <c r="Q15" s="12"/>
       <c r="R15" s="12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="S15" s="13"/>
     </row>
     <row r="16" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="B16" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="K16" s="16"/>
+      <c r="L16" s="16" t="s">
+        <v>20</v>
+      </c>
       <c r="O16" s="33">
-        <v>40000</v>
+        <v>20000</v>
       </c>
       <c r="P16" s="11">
         <f t="shared" si="0"/>
-        <v>0.1532567049808429</v>
+        <v>7.662835249042145E-2</v>
       </c>
       <c r="Q16" s="12"/>
       <c r="R16" s="12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="S16" s="13"/>
     </row>
     <row r="17" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B17" s="6"/>
+      <c r="B17" s="24" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="24" t="s">
+        <v>23</v>
+      </c>
+      <c r="K17" s="37">
+        <v>0.99781732000000001</v>
+      </c>
+      <c r="L17" s="23"/>
       <c r="O17" s="33">
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="P17" s="11">
         <f t="shared" si="0"/>
-        <v>7.662835249042145E-2</v>
+        <v>0.1532567049808429</v>
       </c>
       <c r="Q17" s="12"/>
       <c r="R17" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="S17" s="13"/>
+        <v>42</v>
+      </c>
+      <c r="S17" s="34"/>
     </row>
     <row r="18" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B18" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="O18" s="33">
+      <c r="B18" s="6"/>
+      <c r="I18" s="38"/>
+      <c r="O18" s="18">
         <v>20000</v>
       </c>
-      <c r="P18" s="11">
+      <c r="P18" s="19">
         <f t="shared" si="0"/>
         <v>7.662835249042145E-2</v>
       </c>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="S18" s="13"/>
+      <c r="Q18" s="20"/>
+      <c r="R18" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="S18" s="39"/>
     </row>
     <row r="19" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B19" s="24" t="s">
-        <v>22</v>
-      </c>
-      <c r="F19" s="16"/>
-      <c r="I19" s="5"/>
-      <c r="J19" s="24" t="s">
-        <v>23</v>
-      </c>
-      <c r="K19" s="37">
-        <v>0.99781732000000001</v>
-      </c>
-      <c r="L19" s="23"/>
-      <c r="O19" s="33">
-        <v>40000</v>
-      </c>
-      <c r="P19" s="11">
-        <f t="shared" si="0"/>
-        <v>0.1532567049808429</v>
-      </c>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12" t="s">
-        <v>42</v>
+      <c r="J19" s="40"/>
+      <c r="O19" s="28">
+        <f>SUM(O9:O18)</f>
+        <v>260000</v>
+      </c>
+      <c r="P19" s="9">
+        <f>SUM(P9:P18)</f>
+        <v>0.99616858237547878</v>
       </c>
       <c r="S19" s="34"/>
     </row>
     <row r="20" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="B20" s="6"/>
-      <c r="I20" s="38"/>
-      <c r="O20" s="18">
-        <v>20000</v>
-      </c>
-      <c r="P20" s="19">
-        <f t="shared" si="0"/>
-        <v>7.662835249042145E-2</v>
-      </c>
+      <c r="O20" s="41"/>
+      <c r="P20" s="20"/>
       <c r="Q20" s="20"/>
-      <c r="R20" s="20" t="s">
-        <v>43</v>
-      </c>
-      <c r="S20" s="39"/>
+      <c r="R20" s="42"/>
+      <c r="S20" s="21"/>
     </row>
     <row r="21" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="J21" s="40"/>
-      <c r="O21" s="28">
-        <f>SUM(O11:O20)</f>
-        <v>260000</v>
-      </c>
-      <c r="P21" s="9">
-        <f>SUM(P11:P20)</f>
-        <v>0.99616858237547878</v>
-      </c>
-      <c r="S21" s="34"/>
+      <c r="O21" s="43">
+        <f>O7+O19</f>
+        <v>261000</v>
+      </c>
+      <c r="P21" s="44">
+        <f>P7+P19</f>
+        <v>0.99999999999999989</v>
+      </c>
+      <c r="Q21" s="42"/>
+      <c r="R21" s="42"/>
+      <c r="S21" s="21"/>
     </row>
     <row r="22" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="O22" s="41"/>
-      <c r="P22" s="20"/>
-      <c r="Q22" s="20"/>
-      <c r="R22" s="42"/>
-      <c r="S22" s="21"/>
-    </row>
-    <row r="23" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="O23" s="43">
-        <f>O9+O21</f>
-        <v>261000</v>
-      </c>
-      <c r="P23" s="44">
-        <f>P9+P21</f>
-        <v>0.99999999999999989</v>
-      </c>
-      <c r="Q23" s="42"/>
-      <c r="R23" s="42"/>
-      <c r="S23" s="21"/>
+      <c r="I22" s="38"/>
     </row>
     <row r="24" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="I24" s="38"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="16"/>
+      <c r="L24" s="16"/>
+      <c r="O24" s="45"/>
+    </row>
+    <row r="25" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="22"/>
+      <c r="L25" s="16"/>
+      <c r="O25" s="46"/>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="12"/>
     </row>
     <row r="26" spans="2:19" x14ac:dyDescent="0.2">
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
-      <c r="J26" s="8"/>
-      <c r="K26" s="16"/>
+      <c r="I26" s="22"/>
       <c r="L26" s="16"/>
-      <c r="O26" s="45"/>
+      <c r="O26" s="46"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="12"/>
     </row>
     <row r="27" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="G27" s="6"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="22"/>
-      <c r="L27" s="16"/>
-      <c r="O27" s="46"/>
+      <c r="D27" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="I27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="O27" s="12"/>
       <c r="P27" s="12"/>
       <c r="Q27" s="12"/>
     </row>
     <row r="28" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="22"/>
-      <c r="L28" s="16"/>
-      <c r="O28" s="46"/>
-      <c r="P28" s="12"/>
-      <c r="Q28" s="12"/>
+      <c r="J28" s="16"/>
+      <c r="O28" s="12"/>
     </row>
     <row r="29" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="D29" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="G29" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="I29" s="12"/>
-      <c r="K29" s="12"/>
+      <c r="G29" s="6"/>
+      <c r="J29" s="16"/>
+      <c r="K29" s="22"/>
       <c r="O29" s="12"/>
-      <c r="P29" s="12"/>
-      <c r="Q29" s="12"/>
     </row>
     <row r="30" spans="2:19" x14ac:dyDescent="0.2">
+      <c r="G30" s="6"/>
       <c r="J30" s="16"/>
-      <c r="O30" s="12"/>
+      <c r="L30" s="12"/>
     </row>
     <row r="31" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="G31" s="6"/>
-      <c r="J31" s="16"/>
-      <c r="K31" s="22"/>
-      <c r="O31" s="12"/>
-    </row>
-    <row r="32" spans="2:19" x14ac:dyDescent="0.2">
-      <c r="G32" s="6"/>
-      <c r="J32" s="16"/>
-      <c r="L32" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="22"/>
+      <c r="N31" s="5"/>
+      <c r="O31" s="47"/>
     </row>
     <row r="33" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="L33" s="12"/>
-      <c r="M33" s="22"/>
-      <c r="N33" s="5"/>
       <c r="O33" s="47"/>
     </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="L34" s="12"/>
+      <c r="O34" s="47"/>
+    </row>
     <row r="35" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="O35" s="47"/>
+      <c r="L35" s="12"/>
     </row>
     <row r="36" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="L36" s="12"/>
-      <c r="O36" s="47"/>
+      <c r="E36" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="I36" s="16" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="37" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="L37" s="12"/>
+      <c r="B37" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="O37" s="47"/>
     </row>
     <row r="38" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="E38" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="I38" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="B39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="O39" s="47"/>
+      <c r="R38" s="2" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="40" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="R40" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
-      <c r="O42" s="47"/>
+      <c r="O40" s="47"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="O43" s="47"/>
     </row>
     <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="O45" s="47"/>
     </row>
     <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="O47" s="47"/>
-    </row>
-    <row r="49" spans="15:16" x14ac:dyDescent="0.2">
-      <c r="O49" s="47"/>
-      <c r="P49" s="16"/>
+      <c r="P47" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="O5:S5"/>
+    <mergeCell ref="O3:S3"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="83" orientation="landscape" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="82" orientation="landscape" r:id="rId1"/>
   <headerFooter alignWithMargins="0"/>
   <drawing r:id="rId2"/>
 </worksheet>
